--- a/src/main/resources/templates/template_For_Import.xlsx
+++ b/src/main/resources/templates/template_For_Import.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JavaPrograms\TestProject\src\main\resources\templates\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
   <si>
     <t>Question</t>
   </si>
@@ -70,12 +70,22 @@
   </si>
   <si>
     <t>Comment (Faqat to'g'ri javob uchun)</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Exceldagi test javob E</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -446,10 +456,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05A55F1F-879E-4740-BE22-BEE0EF3E24DE}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultColWidth="31.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="31.5546875" style="2"/>
+    <col min="9" max="16384" style="2" width="31.5546875"/>
+    <col min="8" max="8" style="2" width="31.5546875" customWidth="true"/>
+    <col min="7" max="7" style="2" width="31.5546875" customWidth="true"/>
+    <col min="1" max="5" style="2" width="31.5546875"/>
+    <col min="6" max="6" style="2" width="31.5546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -468,10 +482,13 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" t="s" s="3">
+        <v>14</v>
+      </c>
+      <c r="G1" t="s" s="3">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" t="s" s="3">
         <v>12</v>
       </c>
     </row>
@@ -491,10 +508,13 @@
       <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s" s="1">
         <v>2</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" t="s" s="1">
         <v>11</v>
       </c>
     </row>

--- a/src/main/resources/templates/template_For_Import.xlsx
+++ b/src/main/resources/templates/template_For_Import.xlsx
@@ -459,11 +459,11 @@
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultColWidth="31.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="5" style="2" width="31.5546875"/>
+    <col min="6" max="6" customWidth="true" style="2" width="31.5546875"/>
+    <col min="7" max="7" customWidth="true" style="2" width="31.5546875"/>
+    <col min="8" max="8" customWidth="true" style="2" width="31.5546875"/>
     <col min="9" max="16384" style="2" width="31.5546875"/>
-    <col min="8" max="8" style="2" width="31.5546875" customWidth="true"/>
-    <col min="7" max="7" style="2" width="31.5546875" customWidth="true"/>
-    <col min="1" max="5" style="2" width="31.5546875"/>
-    <col min="6" max="6" style="2" width="31.5546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -520,8 +520,8 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576" xr:uid="{083D6D57-0722-4313-8085-287E416C26E5}">
-      <formula1>$B$1:$E$1</formula1>
+    <dataValidation type="list" sqref="G2:G1048576" allowBlank="true" errorStyle="stop" showErrorMessage="true">
+      <formula1>$B$1:$F$1</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/main/resources/templates/template_For_Import.xlsx
+++ b/src/main/resources/templates/template_For_Import.xlsx
@@ -1,113 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JavaPrograms\TestProject\src\main\resources\templates\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD02C37C-DD14-436F-B59B-D1418897F0A9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EF2D30AB-4CB7-4913-B6BB-3CA9A4955B7A}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
-  <si>
-    <t>Question</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>Correct</t>
-  </si>
-  <si>
-    <t>Exceldagi test savol?</t>
-  </si>
-  <si>
-    <t>Exceldagi test javob A</t>
-  </si>
-  <si>
-    <t>Exceldagi test javob B</t>
-  </si>
-  <si>
-    <t>Exceldagi test javob C</t>
-  </si>
-  <si>
-    <t>Exceldagi test javob D</t>
-  </si>
-  <si>
-    <t>Exceldagi test comment</t>
-  </si>
-  <si>
-    <t>Comment (Faqat to'g'ri javob uchun)</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>Exceldagi test javob E</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
+      <name val="Calibri"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -132,30 +62,89 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -455,75 +444,106 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05A55F1F-879E-4740-BE22-BEE0EF3E24DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="31.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="31.5546875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="5" style="2" width="31.5546875"/>
-    <col min="6" max="6" customWidth="true" style="2" width="31.5546875"/>
-    <col min="7" max="7" customWidth="true" style="2" width="31.5546875"/>
-    <col min="8" max="8" customWidth="true" style="2" width="31.5546875"/>
-    <col min="9" max="16384" style="2" width="31.5546875"/>
+    <col width="31.5546875" customWidth="1" style="2" min="1" max="5"/>
+    <col width="31.5546875" customWidth="1" style="2" min="6" max="6"/>
+    <col width="31.5546875" customWidth="1" style="2" min="7" max="7"/>
+    <col width="31.5546875" customWidth="1" style="2" min="8" max="8"/>
+    <col width="31.5546875" customWidth="1" style="2" min="9" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s" s="3">
-        <v>14</v>
-      </c>
-      <c r="G1" t="s" s="3">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s" s="3">
-        <v>12</v>
+    <row r="1" ht="28.8" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Correct (B yoki B, C)</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Comment (Faqat to'g'ri javob uchun)</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s" s="1">
-        <v>2</v>
-      </c>
-      <c r="H2" t="s" s="1">
-        <v>11</v>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Exceldagi test savol?</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Exceldagi test javob A</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Exceldagi test javob B</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Exceldagi test javob C</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Exceldagi test javob D</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Exceldagi test javob E</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>Exceldagi test comment</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" sqref="G2:G1048576" allowBlank="true" errorStyle="stop" showErrorMessage="true">
-      <formula1>$B$1:$F$1</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>